--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_152_Chile_mainland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_152_Chile_mainland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R7e471e938567402f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R5aab9c331a9d48f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd60fb982def5413e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd756954f42f14535"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra8580d2c2eac4426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf32496eefd374893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3fc1da844d4c4a2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rdb8867c6a8d847cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4d62dc7de7ea42b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re5d792e39b1d4d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc717629aa7b34436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1b17556f347846fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ152CommercialTable" displayName="EEZ152CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ152CommercialTable" displayName="EEZ152CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ152FunctionalTable" displayName="EEZ152FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ152FunctionalTable" displayName="EEZ152FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ152ValidationTable" displayName="EEZ152ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ152ValidationTable" displayName="EEZ152ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -9337,7 +9291,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3644d1dcc18c4d81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92eb66da4324aa8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9347,20 +9301,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9368,714 +9312,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>656453.6225315363</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>50.11872336272725</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>656453.6225315363</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$130,A2,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>32900617.508118242</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>32900617.508118242</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>33878.09256881639</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.286168448889089</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1932.7178108556495</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>33878.09256881639</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2012.8542861702638</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$130,A3,'Species'!$U$2:$U$130))</x:f>
-        <x:v>68191663.83441503</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.286168448889089</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1932.7178108556495</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>65476792.90556786</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2714870.9288471714</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0414631017857368</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.04146310178573683</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>24123.142213002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.714021171400725</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>51.76320653560677</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>24123.142213002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>100.10556127514596</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$130,A4,'Species'!$U$2:$U$130))</x:f>
-        <x:v>2414860.6909527318</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.714021171400725</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>51.76320653560677</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1248691.1926594367</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1166169.498293295</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.9339134488564873</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.9339134488564873</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>462.6312098438</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8747905927350694</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>749.5327139670163</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>462.6312098438</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>805.6496637063337</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$130,A5,'Species'!$U$2:$U$130))</x:f>
-        <x:v>372718.67863071174</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8747905927350694</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>749.5327139670163</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>346757.22628006764</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>25961.452350644104</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.07486924679019</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.07486924679018989</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>368387.87866607716</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1220631729885557</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>13.245341894909071</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>368387.87866607716</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>26.642787012093965</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$130,A6,'Species'!$U$2:$U$130))</x:f>
-        <x:v>9814879.789137408</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1220631729885557</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>13.245341894909071</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4879423.402872471</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>4935456.386264937</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>2.0114835255656396</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.0114835255656396</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>42955.968478907496</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.089445667642728</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.286994606692046</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>42955.968478907496</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>20.128854194533673</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$130,A7,'Species'!$U$2:$U$130))</x:f>
-        <x:v>864654.4262969134</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.089445667642728</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.286994606692046</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>527799.75302557</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>336854.67327134346</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6382243859349137</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6382243859349136</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>80999.87387526801</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.0945230458365995</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>124.31486017746823</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>80999.87387526801</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>638.0989381271476</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$130,A8,'Species'!$U$2:$U$130))</x:f>
-        <x:v>51685933.50824139</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.0945230458365995</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>124.31486017746823</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>10069487.995196505</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>41616445.51304489</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>5.132925679329215</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>4.132925679329214</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>426498.32474615483</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4301377449739543</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>269.238861213241</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>426498.32474615483</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>358.0729296323541</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$130,A9,'Species'!$U$2:$U$130))</x:f>
-        <x:v>152717504.6251468</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4301377449739543</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>269.238861213241</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>114829923.26400977</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>37887581.36113703</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.3299451944597078</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.3299451944597078</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
-        <x:v>1</x:v>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>144.5439770745928</x:v>
       </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$130,A10,'Species'!$U$2:$U$130))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>11987.664587635301</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.7502476209643554</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>56.26620458346324</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>11987.664587635301</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>56.357519479654286</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$130,A11,'Species'!$U$2:$U$130))</x:f>
-        <x:v>675595.0405132184</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.7502476209643554</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>56.26620458346324</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>674500.3881658254</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1094.6523473929847</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0016229084024246</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0016229084024246183</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1819.9267933051</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.0447585408542235</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1108.5583073928838</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1819.9267933051</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1927.6332508158819</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$130,A12,'Species'!$U$2:$U$130))</x:f>
-        <x:v>3508151.4008256337</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.0447585408542235</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1108.5583073928838</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2017494.9655652603</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1490656.4352603734</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.7388650086880006</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.7388650086880005</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>6647.4144558419</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.527897234448304</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>3372.0750700997237</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>6647.4144558419</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>3374.1017478161452</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$130,A13,'Species'!$U$2:$U$130))</x:f>
-        <x:v>22429052.733914465</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.527897234448304</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>3372.0750700997237</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>22415580.56716499</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>13472.166749473661</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0006010179709202</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.000601017970920106</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20b82e819d314a97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e68ff2a54c444be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10085,20 +9565,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10106,1254 +9576,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>35375.5498073437</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.129264353596334</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1346.679824124136</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>35375.5498073437</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1359.3351878204678</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$130,A2,'Species'!$U$2:$U$130))</x:f>
-        <x:v>48087229.64161786</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.129264353596334</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1346.679824124136</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>47639539.19284823</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>447690.448769629</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0093974554824585</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.009397455482458518</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2475.6957442775</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.038293681152733</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1092.1786462157957</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2475.6957442775</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1137.1280790166747</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$130,A3,'Species'!$U$2:$U$130))</x:f>
-        <x:v>2815183.1459200303</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.038293681152733</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1092.1786462157957</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2703902.0264272066</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>111281.11949282372</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.041155751356814</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.041155751356814034</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>88.6407970137</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.22</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1659.5869074375596</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>88.6407970137</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1659.5869074375594</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$130,A4,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>147107.10618876683</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.22</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1659.5869074375596</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>147107.10618876683</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>15144.0251835121</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.160789335197939</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1448.0692629364662</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>15144.0251835121</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1921.2554871682548</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$130,A5,'Species'!$U$2:$U$130))</x:f>
-        <x:v>29095541.48163686</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.160789335197939</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1448.0692629364662</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>21929597.38537965</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7165944.09625721</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.326770435878349</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.326770435878349</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6453.1171593420995</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.52903828458211</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3380.9463912084047</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6453.1171593420995</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3382.646889401407</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$130,A6,'Species'!$U$2:$U$130))</x:f>
-        <x:v>21828616.685991395</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.52903828458211</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3380.9463912084047</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>21817643.171922702</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>10973.514068692923</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0005029651453285</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0005029651453285672</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>63.274719686</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.133872960818129</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1361.0464929154073</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>63.274719686</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1369.135899411879</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$130,A7,'Species'!$U$2:$U$130))</x:f>
-        <x:v>86631.69024732614</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.133872960818129</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1361.0464929154073</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>86119.83531883577</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>511.8549284903711</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0059435195921516</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0059435195921516155</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
-        <x:v>1</x:v>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>144.5439770745928</x:v>
       </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$130,A8,'Species'!$U$2:$U$130))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>550.3173362274999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.451694896822223</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2829.4035677671086</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>550.3173362274999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>3076.5740214524785</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$130,A9,'Species'!$U$2:$U$130))</x:f>
-        <x:v>1693092.0201924553</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.451694896822223</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2829.4035677671086</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1557069.8345261798</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>136022.18566627544</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.087357793883193</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.087357793883193</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>22576.6977935064</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.7450129476876066</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>55.59208307758383</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>22576.6977935064</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>105.57729819850141</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$130,A10,'Species'!$U$2:$U$130))</x:f>
-        <x:v>2383586.7552824738</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.7450129476876066</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>55.59208307758383</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1255085.6593541112</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1128501.0959283626</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.8991426899970387</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.8991426899970387</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>22593.8517934733</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.2600001397368255</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1819.701444109622</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>22593.8517934733</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1819.7014509023788</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$130,A11,'Species'!$U$2:$U$130))</x:f>
-        <x:v>41114064.89005668</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.2600001397368255</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1819.701444109622</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>41114064.73658213</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.15347454696893692</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0000000037328964</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>3.732896466264004e-9</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>116.1485579097</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9939201691322332</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>986.0982069955336</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>116.1485579097</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1079.7653182503332</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$130,A12,'Species'!$U$2:$U$130))</x:f>
-        <x:v>125413.18459568448</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9939201691322332</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>986.0982069955336</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>114533.88469987207</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>10879.299895812408</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0949876093378028</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0949876093378029</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>287.1130472708</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.653489583056217</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>450.2871806155112</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>287.1130472708</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>594.0566000011737</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$130,A13,'Species'!$U$2:$U$130))</x:f>
-        <x:v>170561.4006776677</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.653489583056217</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>450.2871806155112</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>129283.32457349652</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>41278.07610417118</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3192838383476513</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.31928383834765117</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>7183.177107052601</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.34717835136329</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>222.42231230296306</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>7183.177107052601</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>238.16895428017668</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$130,A14,'Species'!$U$2:$U$130))</x:f>
-        <x:v>1710809.7799960228</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.34717835136329</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>222.42231230296306</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1597698.8618323484</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>113110.91816367442</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0707961436699975</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0707961436699975</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>419746.0016306098</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.4197134885073917</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>262.85333314004816</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>419746.0016306098</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>352.3823307285443</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$130,A15,'Species'!$U$2:$U$130))</x:f>
-        <x:v>147911074.36858162</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.4197134885073917</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>262.85333314004816</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>110331635.60081388</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>37579438.76776774</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.3406043838934127</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.3406043838934128</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>0.41019925330000007</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.784000000143345</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>608.1350014794416</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>0.41019925330000007</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>783.9940689422087</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$130,A16,'Species'!$U$2:$U$130))</x:f>
-        <x:v>321.5937816717228</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.784000000143345</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>608.1350014794416</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>249.4565235124614</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>72.13725815926142</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.289177677711274</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.28917767771127406</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>81621.30358631909</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.0828949439874553</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>12.103053247842583</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>81621.30358631909</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>18.508777235215938</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$130,A17,'Species'!$U$2:$U$130))</x:f>
-        <x:v>1510710.5257271118</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.0828949439874553</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>12.103053247842583</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>987866.9834635447</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>522843.5422635671</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.5292651247746267</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.5292651247746267</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1242.0630620495</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.3256695259369766</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>21.167497928224066</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1242.0630620495</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>22.728412878823793</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$130,A18,'Species'!$U$2:$U$130))</x:f>
-        <x:v>28230.122095797175</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.3256695259369766</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>21.167497928224066</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>26291.367292656432</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1938.7548031407423</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0737411174382805</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0737411174382804</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>3132</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.59</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>389.04514499428046</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>3132</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$130,A19,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1218489.3941220865</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.59</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>1218489.3941220865</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>11984.666206761001</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.75</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>56.23413251903491</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>11984.666206761001</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>56.23413251903491</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$130,A20,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>673947.3076673975</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.75</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>56.23413251903491</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>673947.3076673975</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>1021911.5204475449</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.491699058680329</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>31.024090504904702</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>1021911.5204475449</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>41.95458600370857</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$130,A21,'Species'!$U$2:$U$130))</x:f>
-        <x:v>42873874.77279711</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.491699058680329</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>31.024090504904702</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>31703875.498369403</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>11169999.274427705</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.3523228343172808</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.3523228343172809</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>462.6312098438</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.8747905927350694</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>749.5327139670163</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>462.6312098438</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>805.6496637063337</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$130,A22,'Species'!$U$2:$U$130))</x:f>
-        <x:v>372718.67863071174</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.8747905927350694</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>749.5327139670163</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>346757.22628006764</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>25961.452350644104</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.07486924679019</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.07486924679018989</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1206.3347373916</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.854444182610634</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>715.2274640667782</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1206.3347373916</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>1432.7927703741245</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$130,A23,'Species'!$U$2:$U$130))</x:f>
-        <x:v>1728427.6903858525</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.854444182610634</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>715.2274640667782</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>862803.7350402569</x:v>
       </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>865623.9553455956</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>2.0032686695604154</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>1.0032686695604154</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf8bc60f400549b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b4d908d591541e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11528,7 +10184,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -11627,7 +10283,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>345575776.7801696</x:v>
+        <x:v>255387213.71260306</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11641,7 +10297,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>345575776.7801696</x:v>
+        <x:v>286243706.13320345</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11655,7 +10311,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-90188563.0675666</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11669,7 +10325,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-59332070.64696622</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11680,9 +10336,9 @@
         <x:v>EEZ_152</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -11694,47 +10350,19 @@
         <x:v>EEZ_152</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_152</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_152</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R593283ad61094d17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc859d42765d844db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11781,7 +10409,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
